--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2956" uniqueCount="562">
   <si>
     <t>Property</t>
   </si>
@@ -526,6 +526,35 @@
 依頼医を記述した Practitioner  リソースへの参照。</t>
   </si>
   <si>
+    <t>MedicationAdministration.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.extension:drugNumber</t>
+  </si>
+  <si>
+    <t>drugNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_DrugNumber}
+</t>
+  </si>
+  <si>
+    <t>薬剤番号</t>
+  </si>
+  <si>
+    <t>薬剤番号を表現する拡張</t>
+  </si>
+  <si>
     <t>MedicationAdministration.modifierExtension</t>
   </si>
   <si>
@@ -549,9 +578,6 @@
   </si>
   <si>
     <t>MedicationAdministration.identifier</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -582,22 +608,22 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:rpNumber.id</t>
+    <t>MedicationAdministration.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.id</t>
@@ -619,7 +645,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.extension</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.extension</t>
@@ -640,7 +666,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.use</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.use</t>
@@ -677,7 +703,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.type</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.type</t>
@@ -714,16 +740,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.system</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -732,7 +758,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -744,19 +770,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.value</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -768,7 +794,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.period</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.period</t>
@@ -793,7 +819,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:rpNumber.assigner</t>
+    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.assigner</t>
@@ -819,117 +845,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp</t>
-  </si>
-  <si>
-    <t>orderInRp</t>
-  </si>
-  <si>
-    <t>同一RP番号（剤グループ）での薬剤の表記順</t>
-  </si>
-  <si>
-    <t>同一剤グループでの薬剤を表記する際の順番。XML形式と異なりJSON形式の場合、表記順は項目の順序を意味しない。したがって、薬剤の記載順を別に規定する必要があるためIDを用いて表現する。</t>
-  </si>
-  <si>
-    <t>同一剤グループ内での薬剤の順番を1から順の番号で示す。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.id</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.extension</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.use</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.type</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.system</t>
-  </si>
-  <si>
-    <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
-  </si>
-  <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.value</t>
-  </si>
-  <si>
-    <t>RP番号内（剤グループ内）の連番</t>
-  </si>
-  <si>
-    <t>剤グループ内連番。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.period</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:orderInRp.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.instantiates</t>
@@ -2155,7 +2070,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
@@ -3726,43 +3641,41 @@
         <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
       </c>
@@ -3810,7 +3723,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3819,16 +3732,16 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -3842,43 +3755,43 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3915,17 +3828,19 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3937,16 +3852,16 @@
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>79</v>
@@ -3957,46 +3872,46 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -4044,7 +3959,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4056,16 +3971,16 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
@@ -4076,10 +3991,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4090,7 +4005,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -4102,15 +4017,17 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -4147,40 +4064,38 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>79</v>
@@ -4191,14 +4106,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4217,16 +4134,16 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4264,19 +4181,19 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4288,16 +4205,16 @@
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4308,10 +4225,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4328,26 +4245,22 @@
         <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4371,13 +4284,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -4395,7 +4308,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4407,19 +4320,19 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4427,21 +4340,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -4450,23 +4363,21 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4490,55 +4401,55 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4546,10 +4457,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4557,7 +4468,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4566,32 +4477,32 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>79</v>
@@ -4609,13 +4520,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>79</v>
+        <v>213</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4633,7 +4544,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4645,19 +4556,19 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4665,10 +4576,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4676,7 +4587,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -4691,18 +4602,20 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4726,13 +4639,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4750,7 +4663,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4762,19 +4675,19 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4782,10 +4695,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4793,7 +4706,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4808,22 +4721,26 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4865,7 +4782,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4877,19 +4794,19 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4897,10 +4814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4908,7 +4825,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -4923,16 +4840,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4982,7 +4899,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4994,19 +4911,19 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -5014,14 +4931,12 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>79</v>
       </c>
@@ -5030,7 +4945,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -5039,20 +4954,18 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5101,31 +5014,31 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5133,10 +5046,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5156,18 +5069,20 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5216,7 +5131,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5228,19 +5143,19 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5248,14 +5163,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5271,20 +5186,18 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>194</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5321,19 +5234,19 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5345,13 +5258,13 @@
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>191</v>
+        <v>270</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5365,10 +5278,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5379,32 +5292,28 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5428,13 +5337,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5452,31 +5361,31 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>208</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5484,10 +5393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5495,7 +5404,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5504,26 +5413,24 @@
         <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>215</v>
+        <v>279</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5547,13 +5454,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5571,10 +5478,10 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5583,19 +5490,19 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5603,10 +5510,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5614,10 +5521,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5626,29 +5533,25 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>79</v>
@@ -5666,13 +5569,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5690,31 +5593,31 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>231</v>
+        <v>294</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5722,10 +5625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5733,7 +5636,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
@@ -5745,20 +5648,18 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5783,13 +5684,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5807,7 +5708,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5819,19 +5720,19 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5839,10 +5740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5850,7 +5751,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5865,15 +5766,17 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5898,13 +5801,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>307</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5922,10 +5825,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5934,19 +5837,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>247</v>
+        <v>309</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5954,10 +5857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5965,7 +5868,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -5980,16 +5883,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>251</v>
+        <v>313</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>252</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>253</v>
+        <v>315</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6039,10 +5942,10 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -6051,19 +5954,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>256</v>
+        <v>318</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>257</v>
+        <v>320</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -6071,20 +5974,18 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -6099,16 +6000,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>172</v>
+        <v>322</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6158,13 +6059,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -6173,16 +6074,16 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>177</v>
+        <v>325</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>178</v>
+        <v>326</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>179</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6190,10 +6091,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>186</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6204,7 +6105,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -6216,15 +6117,17 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>187</v>
+        <v>330</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>188</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6273,28 +6176,28 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>191</v>
+        <v>333</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>327</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -6305,21 +6208,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>193</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -6328,19 +6231,19 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>335</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>194</v>
+        <v>336</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>195</v>
+        <v>337</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>196</v>
+        <v>338</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6378,43 +6281,43 @@
         <v>79</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>198</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>342</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6422,10 +6325,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>200</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6436,32 +6339,28 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>201</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6485,13 +6384,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6509,31 +6408,31 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>208</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>79</v>
+        <v>347</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>210</v>
+        <v>348</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>132</v>
+        <v>350</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6541,10 +6440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>212</v>
+        <v>351</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6564,23 +6463,19 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6604,13 +6499,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>220</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6628,7 +6523,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6640,19 +6535,19 @@
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6660,21 +6555,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6683,29 +6578,27 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -6747,31 +6640,31 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6779,44 +6672,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>290</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>234</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>292</v>
+        <v>360</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6864,31 +6759,31 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>238</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6896,10 +6791,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>293</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>242</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6919,16 +6814,16 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>244</v>
+        <v>363</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>245</v>
+        <v>364</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6955,13 +6850,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6979,7 +6874,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>246</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6991,19 +6886,19 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>367</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>247</v>
+        <v>368</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -7011,10 +6906,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>369</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>250</v>
+        <v>369</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7022,7 +6917,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -7037,17 +6932,15 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>251</v>
+        <v>370</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>252</v>
+        <v>371</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7096,10 +6989,10 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -7108,19 +7001,19 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>256</v>
+        <v>374</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7128,10 +7021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7151,16 +7044,16 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>296</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>297</v>
+        <v>377</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7187,13 +7080,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>79</v>
+        <v>379</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -7211,7 +7104,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>295</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7226,16 +7119,16 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>298</v>
+        <v>380</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>299</v>
+        <v>381</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7243,10 +7136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>300</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7266,18 +7159,20 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>301</v>
+        <v>384</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>302</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7326,7 +7221,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>300</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7341,27 +7236,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>304</v>
+        <v>387</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>305</v>
+        <v>388</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>306</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>306</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7369,7 +7264,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7378,24 +7273,26 @@
         <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>109</v>
+        <v>392</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>307</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>308</v>
+        <v>394</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7419,13 +7316,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>311</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7443,10 +7340,10 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>306</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>89</v>
@@ -7458,16 +7355,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>312</v>
+        <v>397</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>313</v>
+        <v>398</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>314</v>
+        <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>315</v>
+        <v>399</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7475,10 +7372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7501,15 +7398,17 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>213</v>
+        <v>401</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>317</v>
+        <v>402</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7534,13 +7433,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7558,7 +7457,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>316</v>
+        <v>400</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7573,16 +7472,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>322</v>
+        <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>323</v>
+        <v>404</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>324</v>
+        <v>405</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7590,10 +7489,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>325</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>325</v>
+        <v>406</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7604,7 +7503,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7616,13 +7515,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>213</v>
+        <v>407</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>327</v>
+        <v>409</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7649,13 +7548,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7673,13 +7572,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>325</v>
+        <v>406</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7688,10 +7587,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7705,10 +7604,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7716,7 +7615,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7728,20 +7627,18 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>213</v>
+        <v>344</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>332</v>
+        <v>413</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7766,13 +7663,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7790,10 +7687,10 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>89</v>
@@ -7802,19 +7699,19 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>415</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>338</v>
+        <v>416</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>340</v>
+        <v>79</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7822,10 +7719,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7833,7 +7730,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7845,20 +7742,18 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7907,10 +7802,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>341</v>
+        <v>198</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
@@ -7919,19 +7814,19 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>346</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>348</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7939,21 +7834,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>418</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7965,16 +7860,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>351</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>345</v>
+        <v>176</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8024,31 +7919,31 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>350</v>
+        <v>206</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>355</v>
+        <v>199</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8056,14 +7951,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8076,24 +7971,26 @@
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="N51" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -8141,7 +8038,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8153,16 +8050,16 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>362</v>
+        <v>132</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -8173,10 +8070,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8184,7 +8081,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8196,20 +8093,18 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>364</v>
+        <v>195</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8258,10 +8153,10 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>363</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -8273,16 +8168,16 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8290,10 +8185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8304,7 +8199,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8313,18 +8208,20 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>221</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8349,13 +8246,11 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8373,13 +8268,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -8388,16 +8283,16 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>376</v>
+        <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>377</v>
+        <v>429</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>379</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8405,10 +8300,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8431,13 +8326,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8464,13 +8359,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>79</v>
+        <v>434</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8488,7 +8383,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>190</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8500,19 +8395,19 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>191</v>
+        <v>436</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>79</v>
+        <v>437</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8520,21 +8415,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>438</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8546,18 +8441,20 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8581,13 +8478,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>442</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8605,31 +8502,31 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>198</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>191</v>
+        <v>444</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>79</v>
+        <v>445</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8637,46 +8534,42 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>388</v>
+        <v>196</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8724,25 +8617,25 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>390</v>
+        <v>198</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>140</v>
+        <v>79</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8756,21 +8649,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>447</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>447</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8782,15 +8675,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>392</v>
+        <v>202</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8815,49 +8710,49 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>391</v>
+        <v>206</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>397</v>
+        <v>199</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8871,10 +8766,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8882,10 +8777,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8897,16 +8792,20 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8942,43 +8841,41 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>398</v>
+        <v>454</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>403</v>
+        <v>455</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8986,12 +8883,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9000,7 +8899,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9009,19 +8908,23 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>213</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -9045,13 +8948,11 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>408</v>
+        <v>463</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -9069,7 +8970,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9081,19 +8982,19 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>410</v>
+        <v>455</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9101,10 +9002,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9115,7 +9016,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9127,17 +9028,15 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>413</v>
+        <v>195</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>414</v>
+        <v>196</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9186,53 +9085,53 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>412</v>
+        <v>198</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>417</v>
+        <v>199</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>419</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>420</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9244,20 +9143,18 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>421</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>422</v>
+        <v>202</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>423</v>
+        <v>203</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9293,43 +9190,43 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>420</v>
+        <v>206</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>427</v>
+        <v>199</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>428</v>
+        <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9337,10 +9234,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>429</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9348,10 +9245,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9360,27 +9257,29 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>430</v>
+        <v>103</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>432</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
@@ -9422,31 +9321,31 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9454,10 +9353,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9468,7 +9367,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9477,18 +9376,20 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>436</v>
+        <v>195</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9537,31 +9438,31 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>435</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9569,10 +9470,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9592,19 +9493,21 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>373</v>
+        <v>109</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9652,7 +9555,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9664,19 +9567,19 @@
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>444</v>
+        <v>217</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>79</v>
+        <v>493</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9684,10 +9587,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9707,19 +9610,21 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>381</v>
+        <v>496</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>382</v>
+        <v>497</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
@@ -9767,7 +9672,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>190</v>
+        <v>499</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9779,19 +9684,19 @@
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>191</v>
+        <v>500</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9799,21 +9704,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>447</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>503</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9822,21 +9727,23 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>134</v>
+        <v>504</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>384</v>
+        <v>505</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>385</v>
+        <v>506</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9884,31 +9791,31 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>198</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>191</v>
+        <v>510</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>79</v>
+        <v>511</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9916,45 +9823,47 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>512</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="C67" s="2"/>
+      <c r="C67" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="D67" t="s" s="2">
-        <v>387</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>449</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>388</v>
+        <v>514</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>389</v>
+        <v>515</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>167</v>
+        <v>461</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>168</v>
+        <v>462</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9979,13 +9888,11 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>79</v>
+        <v>516</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -10003,7 +9910,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>390</v>
+        <v>454</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10015,19 +9922,19 @@
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>132</v>
+        <v>455</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -10035,10 +9942,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>449</v>
+        <v>517</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10061,13 +9968,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>450</v>
+        <v>196</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>451</v>
+        <v>197</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10118,7 +10025,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>449</v>
+        <v>198</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10130,13 +10037,13 @@
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>452</v>
+        <v>199</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10150,21 +10057,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -10176,16 +10083,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>454</v>
+        <v>202</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>455</v>
+        <v>203</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>456</v>
+        <v>204</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10211,53 +10118,55 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>457</v>
+        <v>79</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>453</v>
+        <v>206</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>458</v>
+        <v>199</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10265,10 +10174,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10276,7 +10185,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>89</v>
@@ -10288,25 +10197,29 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>213</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>79</v>
+        <v>520</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>79</v>
@@ -10324,13 +10237,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10348,7 +10261,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10360,19 +10273,19 @@
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10380,10 +10293,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>467</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10403,23 +10316,21 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10443,13 +10354,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10467,7 +10378,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10479,19 +10390,19 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>217</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10499,10 +10410,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10522,19 +10433,21 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>188</v>
+        <v>488</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>189</v>
+        <v>489</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10582,7 +10495,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>190</v>
+        <v>491</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10594,19 +10507,19 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>191</v>
+        <v>492</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>79</v>
+        <v>493</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10614,21 +10527,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>523</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10637,21 +10550,21 @@
         <v>79</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>194</v>
+        <v>496</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
@@ -10687,43 +10600,43 @@
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>198</v>
+        <v>499</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>191</v>
+        <v>500</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10731,10 +10644,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10745,7 +10658,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10757,19 +10670,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10806,41 +10719,43 @@
         <v>79</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC74" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10848,14 +10763,12 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10876,19 +10789,19 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>478</v>
+        <v>195</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -10913,11 +10826,13 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -10935,31 +10850,31 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>483</v>
+        <v>530</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>485</v>
+        <v>532</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -10967,10 +10882,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>533</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>494</v>
+        <v>533</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10993,15 +10908,17 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>187</v>
+        <v>534</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>188</v>
+        <v>535</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11050,7 +10967,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>190</v>
+        <v>533</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11059,22 +10976,22 @@
         <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>79</v>
+        <v>538</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>191</v>
+        <v>539</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>79</v>
+        <v>540</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11082,21 +10999,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>495</v>
+        <v>541</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>79</v>
@@ -11108,16 +11025,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>134</v>
+        <v>542</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>194</v>
+        <v>543</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>195</v>
+        <v>544</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>196</v>
+        <v>545</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11155,11 +11072,9 @@
         <v>79</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11167,31 +11082,31 @@
         <v>138</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>198</v>
+        <v>541</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>191</v>
+        <v>547</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>79</v>
+        <v>548</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11199,18 +11114,20 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>549</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11222,29 +11139,27 @@
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>551</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>499</v>
+        <v>552</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>500</v>
+        <v>552</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>503</v>
+        <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>79</v>
@@ -11286,7 +11201,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11295,22 +11210,22 @@
         <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>209</v>
+        <v>554</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>505</v>
+        <v>555</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>506</v>
+        <v>132</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11318,10 +11233,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>507</v>
+        <v>556</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11332,7 +11247,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>79</v>
@@ -11341,19 +11256,19 @@
         <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>187</v>
+        <v>557</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>509</v>
+        <v>558</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>510</v>
+        <v>559</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>511</v>
+        <v>560</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11403,1913 +11318,33 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>513</v>
+        <v>561</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>514</v>
+        <v>79</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="P81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y83" s="2"/>
-      <c r="Z83" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AC93" s="2"/>
-      <c r="AD93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO95" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2956" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="591">
   <si>
     <t>Property</t>
   </si>
@@ -526,35 +526,6 @@
 依頼医を記述した Practitioner  リソースへの参照。</t>
   </si>
   <si>
-    <t>MedicationAdministration.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.extension:drugNumber</t>
-  </si>
-  <si>
-    <t>drugNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_DrugNumber}
-</t>
-  </si>
-  <si>
-    <t>薬剤番号</t>
-  </si>
-  <si>
-    <t>薬剤番号を表現する拡張</t>
-  </si>
-  <si>
     <t>MedicationAdministration.modifierExtension</t>
   </si>
   <si>
@@ -578,6 +549,9 @@
   </si>
   <si>
     <t>MedicationAdministration.identifier</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -608,22 +582,22 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
+    <t>MedicationAdministration.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.id</t>
@@ -645,7 +619,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
+    <t>MedicationAdministration.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.extension</t>
@@ -666,7 +640,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
+    <t>MedicationAdministration.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.use</t>
@@ -703,7 +677,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
+    <t>MedicationAdministration.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.type</t>
@@ -740,16 +714,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
+    <t>MedicationAdministration.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -758,7 +732,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -770,19 +744,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
+    <t>MedicationAdministration.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -794,7 +768,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
+    <t>MedicationAdministration.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.period</t>
@@ -819,7 +793,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
+    <t>MedicationAdministration.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier.assigner</t>
@@ -845,6 +819,117 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID(MedicationRequestからの継承)</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp</t>
+  </si>
+  <si>
+    <t>orderInRp</t>
+  </si>
+  <si>
+    <t>同一RP番号（剤グループ）での薬剤の表記順</t>
+  </si>
+  <si>
+    <t>同一剤グループでの薬剤を表記する際の順番。XML形式と異なりJSON形式の場合、表記順は項目の順序を意味しない。したがって、薬剤の記載順を別に規定する必要があるためIDを用いて表現する。</t>
+  </si>
+  <si>
+    <t>同一剤グループ内での薬剤の順番を1から順の番号で示す。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.id</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.extension</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.use</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.type</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.system</t>
+  </si>
+  <si>
+    <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
+  </si>
+  <si>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.392.100495.20.3.82</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.value</t>
+  </si>
+  <si>
+    <t>RP番号内（剤グループ内）の連番</t>
+  </si>
+  <si>
+    <t>剤グループ内連番。</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.period</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.identifier:orderInRp.assigner</t>
   </si>
   <si>
     <t>MedicationAdministration.instantiates</t>
@@ -2070,7 +2155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO79"/>
+  <dimension ref="A1:AO95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
@@ -3641,41 +3726,43 @@
         <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="N14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>79</v>
       </c>
@@ -3723,7 +3810,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3732,16 +3819,16 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>79</v>
@@ -3755,23 +3842,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>79</v>
@@ -3783,15 +3868,17 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3828,19 +3915,17 @@
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3852,16 +3937,16 @@
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>79</v>
@@ -3872,46 +3957,46 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3959,7 +4044,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3971,16 +4056,16 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>79</v>
@@ -3991,10 +4076,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4005,7 +4090,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>79</v>
@@ -4017,17 +4102,15 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -4064,38 +4147,40 @@
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>79</v>
@@ -4106,16 +4191,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4134,16 +4217,16 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4181,19 +4264,19 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4205,16 +4288,16 @@
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>79</v>
@@ -4225,10 +4308,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4245,22 +4328,26 @@
         <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4284,13 +4371,13 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>79</v>
@@ -4308,7 +4395,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4320,19 +4407,19 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4340,21 +4427,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>79</v>
@@ -4363,21 +4450,23 @@
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4401,55 +4490,55 @@
         <v>79</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>147</v>
+        <v>209</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4457,10 +4546,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4468,7 +4557,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>89</v>
@@ -4477,32 +4566,32 @@
         <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>79</v>
@@ -4520,13 +4609,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>215</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4544,7 +4633,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4556,19 +4645,19 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4576,10 +4665,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4587,7 +4676,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>89</v>
@@ -4602,20 +4691,18 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4639,13 +4726,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4663,7 +4750,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4675,19 +4762,19 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -4695,10 +4782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4706,7 +4793,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>89</v>
@@ -4721,26 +4808,22 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4782,7 +4865,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4794,19 +4877,19 @@
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4814,10 +4897,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4825,7 +4908,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>89</v>
@@ -4840,16 +4923,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>195</v>
+        <v>251</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4899,7 +4982,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4911,19 +4994,19 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4931,12 +5014,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4945,7 +5030,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>79</v>
@@ -4954,18 +5039,20 @@
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>251</v>
+        <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -5014,31 +5101,31 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -5046,10 +5133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>186</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5069,20 +5156,18 @@
         <v>79</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>259</v>
+        <v>187</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -5131,7 +5216,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5143,19 +5228,19 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>265</v>
+        <v>79</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5163,14 +5248,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5186,18 +5271,20 @@
         <v>79</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5234,19 +5321,19 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>198</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5258,13 +5345,13 @@
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>79</v>
@@ -5278,10 +5365,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5292,28 +5379,32 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5337,13 +5428,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5361,31 +5452,31 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>276</v>
+        <v>210</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5393,10 +5484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5404,7 +5495,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
@@ -5413,24 +5504,26 @@
         <v>79</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
       </c>
@@ -5454,13 +5547,13 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>282</v>
+        <v>220</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5478,10 +5571,10 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>221</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>89</v>
@@ -5490,19 +5583,19 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>284</v>
+        <v>210</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>222</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5510,10 +5603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5521,10 +5614,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5533,25 +5626,29 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>79</v>
@@ -5569,13 +5666,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5593,31 +5690,31 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>294</v>
+        <v>231</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>295</v>
+        <v>232</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5625,10 +5722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5636,7 +5733,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>89</v>
@@ -5648,18 +5745,20 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5684,13 +5783,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>299</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5708,7 +5807,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5720,19 +5819,19 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5740,10 +5839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5751,7 +5850,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
@@ -5766,17 +5865,15 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5801,13 +5898,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>307</v>
+        <v>79</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5825,10 +5922,10 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5837,19 +5934,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>247</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5857,10 +5954,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>312</v>
+        <v>250</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5868,7 +5965,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
@@ -5883,16 +5980,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>313</v>
+        <v>251</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>254</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5942,10 +6039,10 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -5954,19 +6051,19 @@
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>318</v>
+        <v>256</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>320</v>
+        <v>257</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5974,18 +6071,20 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -6000,16 +6099,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6059,13 +6158,13 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
@@ -6074,16 +6173,16 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>177</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>326</v>
+        <v>178</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>327</v>
+        <v>179</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>328</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -6091,10 +6190,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6105,7 +6204,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -6117,17 +6216,15 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>188</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6176,28 +6273,28 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>190</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>333</v>
+        <v>191</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>327</v>
+        <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -6208,21 +6305,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>79</v>
@@ -6231,19 +6328,19 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>335</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>336</v>
+        <v>194</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>337</v>
+        <v>195</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>338</v>
+        <v>196</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6281,43 +6378,43 @@
         <v>79</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>198</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>339</v>
+        <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>191</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>342</v>
+        <v>79</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6325,10 +6422,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6339,28 +6436,32 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>344</v>
+        <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6384,13 +6485,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6408,31 +6509,31 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>208</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>348</v>
+        <v>210</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6440,10 +6541,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>351</v>
+        <v>212</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6463,19 +6564,23 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>352</v>
+        <v>214</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6499,13 +6604,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6523,7 +6628,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6535,19 +6640,19 @@
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6555,21 +6660,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>224</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6578,27 +6683,29 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>288</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -6640,31 +6747,31 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6672,46 +6779,44 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>234</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6759,31 +6864,31 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>238</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6791,10 +6896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>293</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>242</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6814,16 +6919,16 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>364</v>
+        <v>245</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6850,13 +6955,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6874,7 +6979,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>362</v>
+        <v>246</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6886,19 +6991,19 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>368</v>
+        <v>247</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>248</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6906,10 +7011,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>369</v>
+        <v>294</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>369</v>
+        <v>250</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6917,7 +7022,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -6932,15 +7037,17 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>370</v>
+        <v>251</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>371</v>
+        <v>252</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6989,10 +7096,10 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>255</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -7001,19 +7108,19 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>374</v>
+        <v>256</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7021,10 +7128,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>295</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7044,16 +7151,16 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>296</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>297</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7080,13 +7187,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -7104,7 +7211,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7119,16 +7226,16 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>380</v>
+        <v>298</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>381</v>
+        <v>299</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7136,10 +7243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7159,20 +7266,18 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7221,7 +7326,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7236,27 +7341,27 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>387</v>
+        <v>304</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>388</v>
+        <v>305</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7264,7 +7369,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7273,26 +7378,24 @@
         <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>392</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7316,13 +7419,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7340,10 +7443,10 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>89</v>
@@ -7355,16 +7458,16 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>397</v>
+        <v>312</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>399</v>
+        <v>315</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7372,10 +7475,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7398,17 +7501,15 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>401</v>
+        <v>213</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>402</v>
+        <v>317</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7433,13 +7534,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7457,7 +7558,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7472,16 +7573,16 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>404</v>
+        <v>323</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7489,10 +7590,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7503,7 +7604,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7515,13 +7616,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>407</v>
+        <v>213</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7548,13 +7649,13 @@
         <v>79</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>79</v>
@@ -7572,13 +7673,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7587,10 +7688,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7604,10 +7705,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7615,7 +7716,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7627,18 +7728,20 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>413</v>
+        <v>332</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7663,13 +7766,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7687,10 +7790,10 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>331</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>89</v>
@@ -7699,19 +7802,19 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>415</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>416</v>
+        <v>338</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7719,10 +7822,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7730,7 +7833,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7742,18 +7845,20 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>195</v>
+        <v>342</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7802,10 +7907,10 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>198</v>
+        <v>341</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
@@ -7814,19 +7919,19 @@
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>79</v>
+        <v>346</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>199</v>
+        <v>347</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7834,21 +7939,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>418</v>
+        <v>350</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>418</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7860,16 +7965,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>351</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>176</v>
+        <v>345</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7919,31 +8024,31 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>206</v>
+        <v>350</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7951,14 +8056,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7971,26 +8076,24 @@
         <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>134</v>
+        <v>359</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -8038,7 +8141,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8050,16 +8153,16 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>132</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>79</v>
@@ -8070,10 +8173,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8081,7 +8184,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8093,18 +8196,20 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>195</v>
+        <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>421</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8153,10 +8258,10 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>89</v>
@@ -8168,16 +8273,16 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>423</v>
+        <v>369</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8185,10 +8290,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8199,7 +8304,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8208,20 +8313,18 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>221</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8246,11 +8349,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>428</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8268,13 +8373,13 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
@@ -8283,16 +8388,16 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>430</v>
+        <v>379</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8300,10 +8405,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8326,13 +8431,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8359,13 +8464,13 @@
         <v>79</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>435</v>
+        <v>79</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>79</v>
@@ -8383,7 +8488,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>431</v>
+        <v>190</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8395,19 +8500,19 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>436</v>
+        <v>191</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>437</v>
+        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8415,21 +8520,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>438</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>438</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8441,20 +8546,18 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>439</v>
+        <v>384</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>439</v>
+        <v>385</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8478,13 +8581,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8502,31 +8605,31 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>438</v>
+        <v>198</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>444</v>
+        <v>191</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8534,42 +8637,46 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>388</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8617,25 +8724,25 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>198</v>
+        <v>390</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8649,21 +8756,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8675,17 +8782,15 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>202</v>
+        <v>392</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8710,49 +8815,49 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>206</v>
+        <v>391</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>199</v>
+        <v>397</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8766,10 +8871,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8777,10 +8882,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8792,20 +8897,16 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8841,41 +8942,43 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>454</v>
+        <v>398</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>455</v>
+        <v>403</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>456</v>
+        <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8883,14 +8986,12 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8899,7 +9000,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8908,23 +9009,19 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>213</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8948,11 +9045,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>463</v>
+        <v>408</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8970,7 +9069,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8982,19 +9081,19 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9002,10 +9101,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9016,7 +9115,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9028,15 +9127,17 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>195</v>
+        <v>413</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>196</v>
+        <v>414</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9085,53 +9186,53 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>198</v>
+        <v>412</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>199</v>
+        <v>417</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -9143,18 +9244,20 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>134</v>
+        <v>421</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>202</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>203</v>
+        <v>423</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9190,43 +9293,43 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>206</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>199</v>
+        <v>427</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9234,10 +9337,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9245,10 +9348,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9257,29 +9360,27 @@
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>430</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>474</v>
+        <v>79</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
@@ -9321,31 +9422,31 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>476</v>
+        <v>433</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>477</v>
+        <v>434</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9353,10 +9454,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>478</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9367,7 +9468,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -9376,20 +9477,18 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>195</v>
+        <v>436</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9438,31 +9537,31 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>483</v>
+        <v>435</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>79</v>
+        <v>439</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>485</v>
+        <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9470,10 +9569,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>486</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9493,21 +9592,19 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>109</v>
+        <v>373</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>488</v>
+        <v>442</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>489</v>
+        <v>443</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>490</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9555,7 +9652,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>441</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9567,19 +9664,19 @@
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>217</v>
+        <v>444</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9587,10 +9684,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9610,21 +9707,19 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>381</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>497</v>
+        <v>382</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
@@ -9672,7 +9767,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>190</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9684,19 +9779,19 @@
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>500</v>
+        <v>191</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9704,21 +9799,21 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>447</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>503</v>
+        <v>447</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9727,23 +9822,21 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>504</v>
+        <v>134</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>505</v>
+        <v>384</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>506</v>
+        <v>385</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9791,31 +9884,31 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>198</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>510</v>
+        <v>191</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>511</v>
+        <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -9823,47 +9916,45 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>512</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="C67" t="s" s="2">
-        <v>513</v>
-      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>79</v>
+        <v>387</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>449</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>388</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>389</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>461</v>
+        <v>167</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>462</v>
+        <v>168</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9888,11 +9979,13 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>516</v>
+        <v>79</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9910,7 +10003,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>454</v>
+        <v>390</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9922,19 +10015,19 @@
         <v>79</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>455</v>
+        <v>132</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>456</v>
+        <v>79</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -9942,10 +10035,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9968,13 +10061,13 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>196</v>
+        <v>450</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>197</v>
+        <v>451</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10025,7 +10118,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>198</v>
+        <v>449</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10037,13 +10130,13 @@
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -10057,21 +10150,21 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -10083,16 +10176,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>202</v>
+        <v>454</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>203</v>
+        <v>455</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>204</v>
+        <v>456</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10118,55 +10211,53 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>206</v>
+        <v>453</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>199</v>
+        <v>458</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>79</v>
+        <v>459</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10174,10 +10265,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>519</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10185,7 +10276,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>89</v>
@@ -10197,29 +10288,25 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>520</v>
+        <v>79</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>79</v>
@@ -10237,13 +10324,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>79</v>
+        <v>464</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10261,7 +10348,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10273,19 +10360,19 @@
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10293,10 +10380,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>467</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10316,21 +10403,23 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10354,13 +10443,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>79</v>
+        <v>471</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10378,7 +10467,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10390,19 +10479,19 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10410,10 +10499,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>522</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10433,21 +10522,19 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>488</v>
+        <v>188</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>489</v>
+        <v>189</v>
       </c>
       <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>490</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10495,7 +10582,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>491</v>
+        <v>190</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10507,19 +10594,19 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>492</v>
+        <v>191</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10527,21 +10614,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>523</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10550,21 +10637,21 @@
         <v>79</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L73" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>498</v>
-      </c>
+      <c r="N73" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
@@ -10600,43 +10687,43 @@
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>499</v>
+        <v>198</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>217</v>
+        <v>147</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>500</v>
+        <v>191</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10644,10 +10731,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10658,7 +10745,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>79</v>
@@ -10670,19 +10757,19 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>504</v>
+        <v>478</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10719,43 +10806,41 @@
         <v>79</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC74" s="2"/>
       <c r="AD74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -10763,12 +10848,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>525</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10789,19 +10876,19 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>195</v>
+        <v>478</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>527</v>
+        <v>489</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>528</v>
+        <v>490</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>529</v>
+        <v>491</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -10826,13 +10913,11 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>79</v>
+        <v>492</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -10850,31 +10935,31 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>530</v>
+        <v>483</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>531</v>
+        <v>484</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>532</v>
+        <v>485</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -10882,10 +10967,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>533</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>533</v>
+        <v>494</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10908,17 +10993,15 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>534</v>
+        <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>535</v>
+        <v>188</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -10967,7 +11050,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>533</v>
+        <v>190</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -10976,22 +11059,22 @@
         <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>538</v>
+        <v>79</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>539</v>
+        <v>191</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>540</v>
+        <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -10999,21 +11082,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>541</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>541</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>79</v>
@@ -11025,16 +11108,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>542</v>
+        <v>134</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>543</v>
+        <v>194</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>544</v>
+        <v>195</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>545</v>
+        <v>196</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11072,9 +11155,11 @@
         <v>79</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="AC77" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="AD77" t="s" s="2">
         <v>79</v>
       </c>
@@ -11082,31 +11167,31 @@
         <v>138</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>541</v>
+        <v>198</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>547</v>
+        <v>191</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>548</v>
+        <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>79</v>
@@ -11114,20 +11199,18 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>549</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11139,27 +11222,29 @@
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>551</v>
+        <v>103</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>79</v>
@@ -11201,7 +11286,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>541</v>
+        <v>504</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11210,22 +11295,22 @@
         <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>554</v>
+        <v>209</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>132</v>
+        <v>506</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -11233,10 +11318,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>556</v>
+        <v>508</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11247,7 +11332,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>79</v>
@@ -11256,19 +11341,19 @@
         <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>557</v>
+        <v>187</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>558</v>
+        <v>509</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>559</v>
+        <v>510</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>560</v>
+        <v>511</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11318,33 +11403,1913 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y83" s="2"/>
+      <c r="Z83" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
+      <c r="N91" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AC93" s="2"/>
+      <c r="AD93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
+      <c r="H95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AK95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -723,7 +723,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -732,7 +732,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -857,7 +857,7 @@
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.value</t>
@@ -911,10 +911,10 @@
     <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
   </si>
   <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値 http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:orderInRp.value</t>
@@ -1581,7 +1581,7 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.30</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodBasicUsage</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1705,7 +1705,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コード</t>
   </si>
   <si>
-    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードurn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
@@ -1720,7 +1720,7 @@
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.system</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.200250.2.2.20.40</t>
+    <t>http://jami.jp/CodeSystem/MedicationMethodDetailUsage</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -268,11 +268,11 @@
     <t>患者への薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -352,10 +352,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -364,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -410,13 +410,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -472,7 +472,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -536,7 +536,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -646,22 +646,22 @@
     <t>MedicationAdministration.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -670,7 +670,7 @@
     <t>Identifier.use</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -687,22 +687,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -726,10 +726,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -781,7 +781,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -806,10 +806,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -833,7 +833,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -851,7 +851,7 @@
     <t>MedicationAdministration.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -866,10 +866,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.period</t>
@@ -1215,7 +1215,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1225,11 +1225,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1238,13 +1238,13 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」(Pafōmansu no shurui)</t>
+    <t>「パフォーマンスの種類」</t>
   </si>
   <si>
     <t>演者の医薬品投与における関与タイプを区別します。 (Ensha no iyakuhin tōyo ni okeru kan'yo taipu o kubetsushimasu.)</t>
   </si>
   <si>
-    <t>「薬物管理を行った個人の役割を説明するコード」</t>
+    <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1263,10 +1263,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰ですか？」(Yakuzaiteiyogyou o okonatta no wa dare desu ka?)</t>
-  </si>
-  <si>
-    <t>「薬剤投与を行った人物または物品を示す」</t>
+    <t>「薬剤投与を行ったのは誰ですか？」</t>
+  </si>
+  <si>
+    <t>薬剤投与を行った人物または物品を示す</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1284,7 +1284,7 @@
     <t>投薬が実施された理由を示すコード</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
+    <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1460,7 +1460,7 @@
     <t>治療剤の患者への内部または表面への投与のルートまたは生理学的経路を指定するコード。例えば、表面的な投与、静注など。</t>
   </si>
   <si>
-    <t>「治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念」</t>
+    <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/route-codes</t>
@@ -1484,7 +1484,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
+    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
@@ -1775,7 +1775,7 @@
     <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1828,7 +1828,7 @@
     <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
@@ -2182,7 +2182,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -268,11 +268,11 @@
     <t>患者への薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
-  </si>
-  <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
+  </si>
+  <si>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
-  </si>
-  <si>
-    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
+    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
+  </si>
+  <si>
+    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>「リソースに関するメタデータ」</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
+    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -355,7 +355,7 @@
     <t>「リソースコンテンツの言語」</t>
   </si>
   <si>
-    <t>リソースが書かれている基本言語。</t>
+    <t>「リソースが書かれている基本言語。」</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>人間の解釈のためのリソースのテキスト要約</t>
-  </si>
-  <si>
-    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
+    <t>「人間の解釈のためのリソースのテキスト要約」</t>
+  </si>
+  <si>
+    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -413,10 +413,10 @@
     <t>「含まれている、インラインのリソース」</t>
   </si>
   <si>
-    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
-  </si>
-  <si>
-    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
+    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
+  </si>
+  <si>
+    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -533,10 +533,10 @@
 user content</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
+    <t xml:space="preserve">無視できない拡張機能 </t>
+  </si>
+  <si>
+    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -833,7 +833,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -1215,7 +1215,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
+    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1225,11 +1225,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>認識されなくても無視できない拡張機能</t>
-  </si>
-  <si>
-    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
+    <t>「認識されなくても無視できない拡張機能」</t>
+  </si>
+  <si>
+    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1241,10 +1241,10 @@
     <t>「パフォーマンスの種類」</t>
   </si>
   <si>
-    <t>演者の医薬品投与における関与タイプを区別します。 (Ensha no iyakuhin tōyo ni okeru kan'yo taipu o kubetsushimasu.)</t>
-  </si>
-  <si>
-    <t>薬物管理を行った個人の役割を説明するコード</t>
+    <t>演者の医薬品投与における関与タイプを区別します。</t>
+  </si>
+  <si>
+    <t>「薬物管理を行った個人の役割を説明するコード」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1266,7 +1266,7 @@
     <t>「薬剤投与を行ったのは誰ですか？」</t>
   </si>
   <si>
-    <t>薬剤投与を行った人物または物品を示す</t>
+    <t>「薬剤投与を行った人物または物品を示す」</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1284,7 +1284,7 @@
     <t>投薬が実施された理由を示すコード</t>
   </si>
   <si>
-    <t>薬剤投与が行われた理由を示すコードのセット。</t>
+    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1460,7 +1460,7 @@
     <t>治療剤の患者への内部または表面への投与のルートまたは生理学的経路を指定するコード。例えば、表面的な投与、静注など。</t>
   </si>
   <si>
-    <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
+    <t>「治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/route-codes</t>
@@ -1484,7 +1484,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
+    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -268,11 +268,11 @@
     <t>患者への薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な出会いと結びつけます。</t>
-  </si>
-  <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+  </si>
+  <si>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,10 +297,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -313,10 +313,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -336,7 +336,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -352,10 +352,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>リソースコンテンツの言語</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -364,7 +364,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -384,10 +384,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -410,13 +410,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>含まれている、インラインのリソース</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>
@@ -533,10 +533,10 @@
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">無視できない拡張機能 </t>
-  </si>
-  <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -833,7 +833,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として投薬実施の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。</t>
   </si>
   <si>
     <t>MedicationAdministration.identifier:requestIdentifier.id</t>
@@ -1009,7 +1009,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>"医薬品投与が取り消された理由を示すコードのセット"</t>
+    <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
@@ -1215,7 +1215,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>MedicationAdministration.performer.modifierExtension</t>
@@ -1225,11 +1225,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1238,13 +1238,13 @@
     <t>MedicationAdministration.performer.function</t>
   </si>
   <si>
-    <t>「パフォーマンスの種類」</t>
+    <t>パフォーマンスの種類</t>
   </si>
   <si>
     <t>演者の医薬品投与における関与タイプを区別します。</t>
   </si>
   <si>
-    <t>「薬物管理を行った個人の役割を説明するコード」</t>
+    <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
@@ -1263,10 +1263,10 @@
 </t>
   </si>
   <si>
-    <t>「薬剤投与を行ったのは誰ですか？」</t>
-  </si>
-  <si>
-    <t>「薬剤投与を行った人物または物品を示す」</t>
+    <t>薬剤投与を行ったのは誰ですか？</t>
+  </si>
+  <si>
+    <t>薬剤投与を行った人物または物品を示す</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1284,7 +1284,7 @@
     <t>投薬が実施された理由を示すコード</t>
   </si>
   <si>
-    <t>「薬剤投与が行われた理由を示すコードのセット。」</t>
+    <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
@@ -1460,7 +1460,7 @@
     <t>治療剤の患者への内部または表面への投与のルートまたは生理学的経路を指定するコード。例えば、表面的な投与、静注など。</t>
   </si>
   <si>
-    <t>「治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念」</t>
+    <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/route-codes</t>
@@ -1484,7 +1484,7 @@
     <t>コード化された値は体内に薬剤が投与される方法を示している。注射ではよく使われる。たとえば、緩徐に注入、深部に静注など。</t>
   </si>
   <si>
-    <t>「薬剤が投与される方法を記述する暗号化された概念。」</t>
+    <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -1772,17 +1772,13 @@
     <t>1回の投与イベントで投与される薬剤の量。この値は、投与が錠剤の飲み込みや注射などの本質的に瞬間的なイベントである場合に使用する。</t>
   </si>
   <si>
-    <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>もし投与速度が即時でない場合、単回の投与期間中に投与される総量を示すことができます。</t>
+  </si>
+  <si>
+    <t>.doseQuantity</t>
+  </si>
+  <si>
+    <t>RXA-6 Administered Amount / RXA-7 Administered Units</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.rate[x]</t>
@@ -1822,17 +1818,13 @@
 </t>
   </si>
   <si>
-    <t>単位時間内での薬剤の容量</t>
-  </si>
-  <si>
-    <t>比率データタイプは、関係を数量と共通単位を使用して適切に表現できない場合にのみ、2つの数値の関係を表現するために使用する必要があります。分母値が「1」に固定されていることが知られている場合、比率ではなく数量を使用する必要があります。 / The Ratio datatype should only be used to express a relationship of two numbers if the relationship cannot be suitably expressed using a Quantity and a common unit.  Where the denominator value is known to be fixed to "1", Quantity should be used instead of Ratio.</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
-  </si>
-  <si>
-    <t>RTO</t>
+    <t>時間当たりの投与量</t>
+  </si>
+  <si>
+    <t>患者に投与されたあるいは投与される薬剤の導入速度を特定します。通常、投与速度は、100 ml / 1時間、または100 ml /時間（時間あたり100 ml）のような輸液の速度として表されます。時間単位あたりの速度として表される場合もあります。例えば、500 ml / 2時間のように。その他の例：200 mcg /分あるいは1分間当たり200 mcg；1リットル/8時間。</t>
+  </si>
+  <si>
+    <t>もしレートが時間の経過とともに変化する場合、かつそれをMedicationAdministrationに取り込む場合は、それぞれの変化を特定のMedicationAdministration.dosage.rateと、レート変更が発生した日時で捉える必要があります。通常、MedicationAdministration.dosage.rate要素は平均レートを伝えるために使用されません。</t>
   </si>
   <si>
     <t>MedicationAdministration.eventHistory</t>
@@ -12941,22 +12933,22 @@
         <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL92" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AK92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL92" t="s" s="2">
+      <c r="AM92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -12964,10 +12956,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12990,16 +12982,16 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13037,7 +13029,7 @@
         <v>79</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
@@ -13047,7 +13039,7 @@
         <v>138</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13065,13 +13057,13 @@
         <v>79</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13079,13 +13071,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C94" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>79</v>
@@ -13107,10 +13099,10 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>581</v>
@@ -13166,7 +13158,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13175,22 +13167,22 @@
         <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>583</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>132</v>
+        <v>576</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>79</v>
@@ -13198,10 +13190,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13224,16 +13216,16 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13283,7 +13275,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13301,7 +13293,7 @@
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -1327,7 +1327,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -2150,17 +2150,17 @@
   <dimension ref="A1:AO95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="68.30859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="58.66015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.1484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.5625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.2890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="193.69921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="166.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2169,27 +2169,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.23046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.6171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="101.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="22.50390625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="19.29296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -268,7 +268,7 @@
     <t>患者への薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な受療行動と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -705,7 +705,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -799,7 +799,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1012,7 +1012,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1036,7 +1036,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1134,7 +1134,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1287,7 +1287,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1356,7 +1356,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1463,7 +1463,7 @@
     <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1487,7 +1487,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1785,7 +1785,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1830,7 +1830,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -1423,7 +1423,7 @@
     <t>フリーテキストの投与方法の説明　SIG:用法</t>
   </si>
   <si>
-    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコーディングできない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
+    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコード化できない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
 投与量や用法のこの指示は、実際に投与される薬の投与量や用法を反映する必要がある。</t>
   </si>
   <si>
@@ -1542,7 +1542,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationadministration.xlsx
@@ -563,7 +563,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1383,7 +1383,7 @@
   </si>
   <si>
     <t>構造化された注釈情報がないシステムの場合、この要素によって作成者や作成時刻情報なしで単一の注釈を簡単に伝達できる。投与情報に付帯する潜在的な情報や修飾的な情報を伝えるために、この要素に叙述的な記述でそれらを含める必要がある場合がある。   
-*注釈は、計算可能な「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDである）。</t>
+*注釈は、計算可能な「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDである）。</t>
   </si>
   <si>
     <t>Event.note</t>
